--- a/data.xlsx
+++ b/data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
   <si>
     <t>question</t>
   </si>
@@ -41,28 +41,6 @@
   </si>
   <si>
     <t>二、现任监事三、现任高级管理人员日40 3、董事、监事、高级管理人员报酬情况董事、监事、高级管理人员报酬的决策程序、确定依据、实际支付情况公司董事（不含独立董事）、监事、高级管理人员及其他核心人员的薪酬由工资、奖金、社会保险和住房公积金组成，薪酬水平由个人学历、工作经验、岗位职责等综合因素并参考同行业水平确定，公司为每位独立董事提供年度津贴。公司根据有关法律法规的要求设立薪酬与考核委员会，负责包括非独立董事、高级经理人员在内的薪酬相关事宜。薪酬与考核委员会由3名董事组成，独立董事占多数。公司董事会制定了《董事会薪酬与考核委员会工作细则》，并严格遵照执行。薪酬与考核委员会根据公司非独立董事及高级管理人员管理岗位的主要范围、职责、重要性以及其他相关企业相关岗位的薪酬水平制定薪酬计划或方案，包括绩效评价标准、程序及主要评价体系，奖励和惩罚的主要方案和制度等，并对公司薪酬制度执行情况进行监督。公司报告期内董事、监事和高级管理人员报酬情况八、报告期内董事履行职责的情况1、本报告期董事会情况无3、董事对公司有关事项提出异议的情况董事对公司有关事项是否提出异议□是☑否报告期内董事对公司有关事项未提出异议。4、董事履行职责的其他说明提出的重其他履行异议事项具体情况（如要意见和况职责的情建议有）十、监事会工作情况□是☑否监事会对报告期内的监督事项无异议。十一、公司员工情况1、员工数量、专业构成及教育程度3,6153,6152、薪酬政策公司已制定了包括《安克创新项目奖金管理总则》《安克转岗定薪规则》《安克年度调薪方案流程》等具体规则在内的员工薪酬管理制度，旨在通过合理的薪酬制度和科学的管理、分配，达到增强公司的凝聚力，建立稳定的员工队伍，吸引高素质的人才，激发员工工作热情的目的。该制度主要包括制度原则、薪酬结构、薪酬调整、薪酬发放等内容。公司未来薪酬制度的主体框架将延续目前的薪酬制度，并根据公司的发展情况予以修订。公司未来会在参照行业和地区就业市场薪酬制度和薪酬体系的基础上，结合公司自身发展情况和劳动力市场供求状况对薪酬制度进行合理调整，同时会更加注重员工岗位效能和岗位价值的评估，进一步完善激励性的薪酬体系建设。根据公司现有的薪酬制度及未来的公司业务发展规划及人员招聘计划等，预计公司的平均员工薪酬将与公司的业务发展趋势相匹配，保持相对稳定的增长趋势。</t>
-  </si>
-  <si>
-    <t>阳萌
-贺丽
-LP:23.90%
-LP40.41%
-LP:25.02%
-LP:39.73%
-44.04%
-远修咨询
-远清咨询
-远景咨询
-远帆咨询
-3.70%
-0.43%
-0.05%
-1.08%
-0.27%
-安克创新科技股份有限公司</t>
-  </si>
-  <si>
-    <t>标，从而将旗下品牌陆续打造成为各自品类的全球化领导品牌。（3）继续深耕发达国家市场，持续拓展新兴经济市场2023年，公司将继续实施市场开发计划，在巩固现有市场的基础上积极拓展新兴经济市场。一方面，公司将巩固主要发达国家和地区市场，扩大产品在北美、欧洲、日本、中东和澳洲等国家和地区中的市场份额，提升公司品牌在上述国家和地区市场中的知名度和美誉度。未来公司将继续通过亚马逊以及其本土大型超市、卖场等销售渠道加大市场扩展力度，并综合各个品类发展阶段及其业务运行模式特点，在相应市场深化渠道建设并精细销售运营管理。另一方面，公司将把握新兴经济国家和地区结构性复苏机会，通过拓展销售覆盖面以及强化渠道竞争力等方式，继续拓展新兴市场，并提升在此类市场的品牌知名度和市场占有率。其中，中国市场、东南亚市场以及拉丁美洲区域市场仍将是公司未来持续布局的重点区域。（4）持续改进产品设计和品质管理能力，为客户提供高质量的优质产品2023年，公司拟基于现有的硬件检测能力，在产品品类愈加丰富、设计构造愈加复杂的情况下继续增加更为全面的检测项目，持续提高产品质量检测的效率和准确度。公司将进一步完善全面质量管理相关部门的协同合作，对产品从开发到生命周期端到端加强质量管理，支撑产品高品质目标达成；细化产品质量标准体系建设，对产品设计、研发和销售等消费电子产品各环节深入规范监督和控制，加快形成稳定、有序、高质、高效的经营管理模式，将优质产品推向市场。（5）深度融合可持续发展理念，实施减碳举措和拥抱碳中和2023年，公司将进一步深度融合可持续发展的理念，践行全面环保战略，更好地履行作为全球化消费电子品牌企业的责任与担当。在主营业务上，深度提升能源转化效率，和推行基于光伏新能源技术的便携式和户用储能电源及管理设备应用。在供应链端，产品材质方面，公司已于2022年推出了首款基于生物基材质的环保产品，后续计划在此基础上持续突破，探索消费电子产品主材质环保化的可能；在包装方面，安克创新将通过创新寻源和设计，不断深化极简化包装和减塑包装的应用，减少不必要的塑料浪费。在碳中和端，安克创新已经和全球领先的环保机构启动合作，计划实施一系列碳中和计划。</t>
   </si>
   <si>
     <t>&lt;table&gt;&lt;caption&gt;（1）企业集团的构成&lt;/caption&gt;
@@ -96,7 +74,24 @@
 &lt;/table&gt;</t>
   </si>
   <si>
-    <t>3、培训计划公司高度重视人才团队的建设与培养，将“打造学习型组织”纳入了企业发展战略，并建立了一整套人才培养计划和人才发展体系，希望于与员工实现“共成长”。公司成立了“安克创新赋能中心”，通过新人入职培训、一对一“导师制”帮助，岗位技能培训、通用技能配件、管理技能培训等全方位培训，与高度赋能、充分放权的工作和人才培养理念相结合，让人才和团队既有理论知识的输入习得，又有执行实践的验证提升，共同打造一个“学习型组织”，通过每一位人才的提升，实现企业经营管理水平的持续提升。4、劳务外包情况十二、公司利润分配及资本公积金转增股本情况报告期内利润分配政策，特别是现金分红政策的制定、执行或调整情况公司报告期利润分配预案及资本公积金转增股本预案与公司章程和分红管理办法等的相关规定一致☑是□否公司报告期利润分配预案及资本公积金转增股本预案符合公司章程等的相关规定。本年度利润分配及资本公积金转增股本情况十三、公司股权激励计划、员工持股计划或其他员工激励措施的实施情况1、股权激励报告期内，公司推出了2022年限制性股票激励计划，具体情况如下：（1）公司于2022年6月20日召开第三届董事会第二次会议、于2022年7月7日召开2022年第三次临时股东大会，审议通过了《关于公司〈2022年限制性股票激励计划（草案）〉及其摘要的议案》《关于公司〈2022年限制性股票激励计划实施考核管理办法〉的议案》。公司第三届监事会第二次会议对公司《2022年限制性股票激励计划（草案）》激励对象名单进行了核查。（2）公司于2022年7月12日召开第三届董事会第三次会议和第三届监事会第三次会议，审议通过了《关于调整2022年限制性股票激励计划首次授予激励对象名单及授予数量的议案》《关于向2022年限制性股票激励计划激励对象首次授予限制性股票的议案》，同意以2022年7月12日为首次授予日，以40.00元/股的价格向424 名激励对象授予5,183,420股第二类限制性股票，其中，高级管理人员祝芳浩、张希和杨帆分别获授100.85、6.65和2.72万股。（3）公司于2022年8月23日召开第三届董事会第五次会议和第三届监事会第四次会议，审议通过了《关于向激励对象授予2022年限制性股票激励计划部分预留限制性股票的议案》，同意以2022年8月24日为授予日，以40.00元/股的价格向12名激励对象授予381,033股第二类限制性股票。</t>
+    <t>&lt;table&gt;&lt;caption&gt;七、董事、监事和高级管理人员情况1、基本情况&lt;/caption&gt;
+&lt;tr&gt;&lt;th  &gt;姓名&lt;/th&gt;&lt;th  &gt;职务&lt;/th&gt;&lt;th  &gt;任职 性别 状态&lt;/th&gt;&lt;th  &gt;年龄&lt;/th&gt;&lt;th  &gt;任期起 始日期&lt;/th&gt;&lt;th  &gt;任期终止&lt;/th&gt;&lt;th  &gt;日期&lt;/th&gt;&lt;th  &gt;期初持 股数 （股）&lt;/th&gt;&lt;th  &gt;本期增 持股份 数量 （股）&lt;/th&gt;&lt;th  &gt;本期减 持股份 数量 （股）&lt;/th&gt;&lt;th  &gt;其他 增减 变动 （股 ）&lt;/th&gt;&lt;th  &gt;期末 股份 持股 增减 数 变动 （股 的原 因&lt;/th&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td  &gt;阳萌&lt;/td&gt;&lt;td  &gt;董事长&lt;/td&gt;&lt;td  &gt;现任 男&lt;/td&gt;&lt;td  &gt;41 &lt;/td&gt;&lt;td  &gt;2016年 05月 12日&lt;/td&gt;&lt;td  &gt;2025年 06月01 日&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;178,974 ,000 &lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;178,97 4,000&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td  &gt;赵东平&lt;/td&gt;&lt;td  &gt;董事、 总经理&lt;/td&gt;&lt;td  &gt;现任 男&lt;/td&gt;&lt;td  &gt;47 &lt;/td&gt;&lt;td  &gt;2016年 05月 12日&lt;/td&gt;&lt;td  &gt;2025年 06月01 日&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;48,700, 000 &lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;48,700 ,000&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td  &gt;张山峰&lt;/td&gt;&lt;td  &gt;董事、 副总经 理&lt;/td&gt;&lt;td  &gt;现任 男&lt;/td&gt;&lt;td  &gt;41 &lt;/td&gt;&lt;td  &gt;2016年 05月 12日&lt;/td&gt;&lt;td  &gt;2025年 06月01 日&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;6,923,0 79 &lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;6,923, 079&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td  &gt;高韬&lt;/td&gt;&lt;td  &gt;董事&lt;/td&gt;&lt;td  &gt;现任 男&lt;/td&gt;&lt;td  &gt;45 &lt;/td&gt;&lt;td  &gt;2016年 05月 12日&lt;/td&gt;&lt;td  &gt;2025年 06月01 日&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;9,725,1 37 &lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;740,000 &lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;8,985,股票 137 减持&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td  &gt;连萌 祝芳浩&lt;/td&gt;&lt;td  &gt;董事 董事&lt;/td&gt;&lt;td  &gt;现任 男 现任 男&lt;/td&gt;&lt;td  &gt;44  48 &lt;/td&gt;&lt;td  &gt;2017年 04月 11日 2021年 05月 27日&lt;/td&gt;&lt;td  &gt;2025年 06月01 日 2025年 06月01 日&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td  &gt;邓海峰&lt;/td&gt;&lt;td  &gt;独立董 事&lt;/td&gt;&lt;td  &gt;现任 男&lt;/td&gt;&lt;td  &gt;48 &lt;/td&gt;&lt;td  &gt;2018年 01月 08日&lt;/td&gt;&lt;td  &gt;2025年 06月01 日&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td  &gt;李国强 高文进&lt;/td&gt;&lt;td  &gt;独立董 事 独立董 事&lt;/td&gt;&lt;td  &gt;现任 男 现任 男&lt;/td&gt;&lt;td  &gt;44  62 &lt;/td&gt;&lt;td  &gt;2018年 01月 08日 2021年 03月 09日&lt;/td&gt;&lt;td  &gt;2024年 01月07 日 2025年 06月01 日&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td  &gt;杨婷 刘枚清&lt;/td&gt;&lt;td  &gt;监事会 主席 监事&lt;/td&gt;&lt;td  &gt;现任 女 现任 女&lt;/td&gt;&lt;td  &gt;7  28 &lt;/td&gt;&lt;td  &gt;2022年 06月 02日 2022年 06月 02日&lt;/td&gt;&lt;td  &gt;2025年 06月01 日 2025年 06月01 日&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td  &gt;曾旖&lt;/td&gt;&lt;td  &gt;监事&lt;/td&gt;&lt;td  &gt;现任 女&lt;/td&gt;&lt;td  &gt;30 &lt;/td&gt;&lt;td  &gt;2022年 06月 02日&lt;/td&gt;&lt;td  &gt;2025年 06月01 日&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td  &gt;张希 杨帆&lt;/td&gt;&lt;td  &gt;董事会 秘书 财务负 责人&lt;/td&gt;&lt;td  &gt;现任 男 现任 男&lt;/td&gt;&lt;td  &gt;41  36 &lt;/td&gt;&lt;td  &gt;2020年 08月 27日 2021年 02月 19日&lt;/td&gt;&lt;td  &gt;2025年 06月01 日 2025年 06月01 日&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td  &gt;黄思敏 毛艳红&lt;/td&gt;&lt;td  &gt;监事会 主席 监事&lt;/td&gt;&lt;td  &gt;离任 女 离任 女&lt;/td&gt;&lt;td  &gt;34  38 &lt;/td&gt;&lt;td  &gt;2019年 05月 10日 2017年 01月 11日&lt;/td&gt;&lt;td  &gt;2022年 06月02 日 2022年 06月02 日&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;2017年2022年&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td  &gt;胡一杰&lt;/td&gt;&lt;td  &gt;监事&lt;/td&gt;&lt;td  &gt;离任 女&lt;/td&gt;&lt;td  &gt;37 &lt;/td&gt;&lt;td  &gt;01月&lt;/td&gt;&lt;td  &gt;06月02&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;11日&lt;/td&gt;&lt;td  &gt;日&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td  &gt;合计&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;244,322 ,216 &lt;/td&gt;&lt;td  &gt;0 &lt;/td&gt;&lt;td  &gt;740,000 &lt;/td&gt;&lt;td  &gt;0 &lt;/td&gt;&lt;td  &gt;243,58 2,216 &lt;/td&gt;&lt;/tr&gt;
+&lt;/table&gt;</t>
   </si>
 </sst>
 </file>
@@ -454,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -482,7 +477,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>5.31465</v>
+        <v>4.6991854</v>
       </c>
       <c r="D2">
         <v>0.4292499206848461</v>
@@ -499,7 +494,7 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>3.1884935</v>
+        <v>2.4234862</v>
       </c>
       <c r="D3">
         <v>0.3633079783843504</v>
@@ -516,10 +511,10 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>0.7777371</v>
+        <v>3.2668607</v>
       </c>
       <c r="D4">
-        <v>0.2400612479589849</v>
+        <v>0.09219619882783585</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -533,47 +528,13 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>0.7311666</v>
+        <v>1.1536229</v>
       </c>
       <c r="D5">
-        <v>0.2125587552724714</v>
+        <v>0.02182282497345924</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>3.195942</v>
-      </c>
-      <c r="D6">
-        <v>0.09219619882783585</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>0.7692536</v>
-      </c>
-      <c r="D7">
-        <v>0.07504072453849712</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>question</t>
   </si>
@@ -29,69 +29,6 @@
   </si>
   <si>
     <t>doc</t>
-  </si>
-  <si>
-    <t>安克创新研发人员年龄构成</t>
-  </si>
-  <si>
-    <t>2023-04-19安克创新：2022年年度报告</t>
-  </si>
-  <si>
-    <t>编制单位：安克创新科技股份有限公司2022年12月31日84编制单位：安克创新科技股份有限公司2022年度编制单位：安克创新科技股份有限公司2022年度编制单位：安克创新科技股份有限公司2022年度编制单位：安克创新科技股份有限公司2022年度7、合并所有者权益变动表编制单位：安克创新科技股份有限公司2022年度8、母公司所有者权益变动表编制单位：安克创新科技股份有限公司2022年度三、公司基本情况安克创新科技股份有限公司(以下简称“本公司”或“公司”)是在湖南省长沙市成立的股份有限公司。本公司于2020年8月以每股人民币66.32元(每股面值1.00元)发行人民币普通股(A股)股票41,000,000股并在深圳证券交易所上市。本公司的控股股东为阳萌先生，共同实际控制人为阳萌先生和贺丽女士，二者为夫妻关系。本公司及子公司(以下简称“本集团”)属于计算机、通信和其他电子设备制造业行业。主要经营自有品牌移动设备周边产品、智能硬件产品等消费电子产品的自主研发、设计和销售。产品主要为充电类、无线音频类、智能创新类等消费电子产品。本报告期内，本集团子公司的情况参见附注八和九。四、财务报表的编制基础本公司以持续经营为基础编制财务报表。本集团自2019年1月1日和2020年1月1日起分别执行了中华人民共和国财政部(以下简称“财政部”)2017年度修订的《企业会计准则第22号——金融工具确认和计量》等新金融工具准则和《企业会计准则第14号——收入》，并自2021年1月1日起执行了财政部2018年度修订的《企业会计准则第21号——租赁》(参见附注五、26(1))。五、重要会计政策及会计估计1、遵循企业会计准则的声明2、会计期间会计年度自公历1月1日起至12月31日止。本报告期间为2022年1月1日至2022年12月31日。3、营业周期本公司将从购买用于加工的资产起至实现现金或现金等价物的期间作为正常营业周期。本公司营业周期短于一年。4、记账本位币本公司的记账本位币为人民币，编制财务报表采用的货币为人民币。本公司及子公司选定记账本位币的依据是主要业务收支的计价和结算币种。本公司的部分子公司采用本公司记账本位币以外的货币作为记账本位币，在编制本财务报表时，这些子公司的外币财务报表按照附注五、8进行了折算。5、同一控制下和非同一控制下企业合并的会计处理方法本集团取得对另一个或多个企业(或一组资产或净资产)的控制权且其构成业务的，该交易或事项构成企业合并。企业合并分为同一控制下的企业合并和非同一控制下的企业合并。对于非同一控制下的交易，购买方在判断取得的资产组合等是否构成一项业务时，将考虑是否选择采用“集中度测试”的简化判断方式。如果该组合通过集中度测试，则判断为不构成业务。如果该组合未通过集中度测试，仍应按照业务条件进行判断。当本集团取得了不构成业务的一组资产或净资产时，应将购买成本按购买日所取得各项可辨认资产、负债的相对公允价值基础进行分配，不按照以下企业合并的会计处理方法进行处理。</t>
-  </si>
-  <si>
-    <t>二、现任监事三、现任高级管理人员日40 3、董事、监事、高级管理人员报酬情况董事、监事、高级管理人员报酬的决策程序、确定依据、实际支付情况公司董事（不含独立董事）、监事、高级管理人员及其他核心人员的薪酬由工资、奖金、社会保险和住房公积金组成，薪酬水平由个人学历、工作经验、岗位职责等综合因素并参考同行业水平确定，公司为每位独立董事提供年度津贴。公司根据有关法律法规的要求设立薪酬与考核委员会，负责包括非独立董事、高级经理人员在内的薪酬相关事宜。薪酬与考核委员会由3名董事组成，独立董事占多数。公司董事会制定了《董事会薪酬与考核委员会工作细则》，并严格遵照执行。薪酬与考核委员会根据公司非独立董事及高级管理人员管理岗位的主要范围、职责、重要性以及其他相关企业相关岗位的薪酬水平制定薪酬计划或方案，包括绩效评价标准、程序及主要评价体系，奖励和惩罚的主要方案和制度等，并对公司薪酬制度执行情况进行监督。公司报告期内董事、监事和高级管理人员报酬情况八、报告期内董事履行职责的情况1、本报告期董事会情况无3、董事对公司有关事项提出异议的情况董事对公司有关事项是否提出异议□是☑否报告期内董事对公司有关事项未提出异议。4、董事履行职责的其他说明提出的重其他履行异议事项具体情况（如要意见和况职责的情建议有）十、监事会工作情况□是☑否监事会对报告期内的监督事项无异议。十一、公司员工情况1、员工数量、专业构成及教育程度3,6153,6152、薪酬政策公司已制定了包括《安克创新项目奖金管理总则》《安克转岗定薪规则》《安克年度调薪方案流程》等具体规则在内的员工薪酬管理制度，旨在通过合理的薪酬制度和科学的管理、分配，达到增强公司的凝聚力，建立稳定的员工队伍，吸引高素质的人才，激发员工工作热情的目的。该制度主要包括制度原则、薪酬结构、薪酬调整、薪酬发放等内容。公司未来薪酬制度的主体框架将延续目前的薪酬制度，并根据公司的发展情况予以修订。公司未来会在参照行业和地区就业市场薪酬制度和薪酬体系的基础上，结合公司自身发展情况和劳动力市场供求状况对薪酬制度进行合理调整，同时会更加注重员工岗位效能和岗位价值的评估，进一步完善激励性的薪酬体系建设。根据公司现有的薪酬制度及未来的公司业务发展规划及人员招聘计划等，预计公司的平均员工薪酬将与公司的业务发展趋势相匹配，保持相对稳定的增长趋势。</t>
-  </si>
-  <si>
-    <t>&lt;table&gt;&lt;caption&gt;（1）企业集团的构成&lt;/caption&gt;
-&lt;tr&gt;&lt;th  &gt;子公司名称&lt;/th&gt;&lt;th  rowspan=2 &gt;主要经营 地 深圳&lt;/th&gt;&lt;th  rowspan=2 &gt;注册地 深圳&lt;/th&gt;&lt;th  rowspan=2 &gt;业务性质 研发&lt;/th&gt;&lt;th colspan=2 &gt;持股比例 直接 间接&lt;/th&gt;&lt;th colspan=2 &gt;取得方式&lt;/th&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;深圳海翼智新科技有限公司&lt;/td&gt;&lt;td  &gt;75.14% &lt;/td&gt;&lt;td  &gt;1.10% &lt;/td&gt;&lt;td  &gt;同一控制下企业合并取得的子公司&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;深圳海翼翱翔科技有限公司&lt;/td&gt;&lt;td  &gt;深圳&lt;/td&gt;&lt;td  &gt;深圳&lt;/td&gt;&lt;td  &gt;研发&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;同一控制下企业合并取得的子公司&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;Anker HoldingLimited &lt;/td&gt;&lt;td  &gt;开曼群岛&lt;/td&gt;&lt;td  &gt;开曼群岛&lt;/td&gt;&lt;td  &gt;投资&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;同一控制下企业合并取得的子公司&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;Anker Innovations Limited &lt;/td&gt;&lt;td  &gt;香港&lt;/td&gt;&lt;td  &gt;香港&lt;/td&gt;&lt;td  &gt;采购&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;同一控制下企业合并取得的子公司&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;Anker JapanCo., Ltd. &lt;/td&gt;&lt;td  &gt;日本&lt;/td&gt;&lt;td  &gt;日本&lt;/td&gt;&lt;td  &gt;销售&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;同一控制下企业合并取得的子公司&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;Anker Technology (UK)Ltd. &lt;/td&gt;&lt;td  &gt;英国&lt;/td&gt;&lt;td  &gt;英国&lt;/td&gt;&lt;td  &gt;销售&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;同一控制下企业合并取得的子公司&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;Fantasia Trading LLC &lt;/td&gt;&lt;td  &gt;美国&lt;/td&gt;&lt;td  &gt;美国&lt;/td&gt;&lt;td  &gt;销售&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;同一控制下企业合并取得的子公司&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;Power Mobile Life LLC &lt;/td&gt;&lt;td  &gt;美国&lt;/td&gt;&lt;td  &gt;美国&lt;/td&gt;&lt;td  &gt;销售&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;同一控制下企业合并取得的子公司&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;天津海翼远扬管理咨询合伙企业（有限合伙）（注）&lt;/td&gt;&lt;td  &gt;天津&lt;/td&gt;&lt;td  &gt;天津&lt;/td&gt;&lt;td  &gt;投资&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;4.42% &lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;设立&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;天津远弘智新管理咨询合伙企业（有限合伙）（注）&lt;/td&gt;&lt;td  &gt;天津&lt;/td&gt;&lt;td  &gt;天津&lt;/td&gt;&lt;td  &gt;投资&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;3.23% &lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;设立&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;湖南安克智瑞制造有限公司&lt;/td&gt;&lt;td  &gt;湖南&lt;/td&gt;&lt;td  &gt;湖南&lt;/td&gt;&lt;td  &gt;销售&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;设立&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;湖南安克电子科技有限公司&lt;/td&gt;&lt;td  &gt;湖南&lt;/td&gt;&lt;td  &gt;湖南&lt;/td&gt;&lt;td  &gt;销售&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;设立&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;海翼智慧供应链管理（深圳）有限公司&lt;/td&gt;&lt;td  &gt;深圳&lt;/td&gt;&lt;td  &gt;深圳&lt;/td&gt;&lt;td  &gt;销售&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;设立&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;深圳市安克智造科技有限公司&lt;/td&gt;&lt;td  &gt;深圳&lt;/td&gt;&lt;td  &gt;深圳&lt;/td&gt;&lt;td  &gt;研发&lt;/td&gt;&lt;td  &gt;60.00% &lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;设立&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;湖南海翼电子商务有限公司&lt;/td&gt;&lt;td  &gt;湖南&lt;/td&gt;&lt;td  &gt;湖南&lt;/td&gt;&lt;td  &gt;销售&lt;/td&gt;&lt;td  &gt;90.00% &lt;/td&gt;&lt;td  &gt;10.00% &lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;设立&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;安克创新商务服务（海南）有限公司&lt;/td&gt;&lt;td  &gt;海南&lt;/td&gt;&lt;td  &gt;海南&lt;/td&gt;&lt;td  &gt;销售&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;设立&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;Smart Innovation LLC &lt;/td&gt;&lt;td  &gt;美国&lt;/td&gt;&lt;td  &gt;美国&lt;/td&gt;&lt;td  &gt;投资&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;设立&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;Anker Innovations DMCC &lt;/td&gt;&lt;td  &gt;阿拉伯联 合酋长国&lt;/td&gt;&lt;td  &gt;阿拉伯联 合酋长国&lt;/td&gt;&lt;td  &gt;销售&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;设立&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;Anker Innovations Deutschland Gmbh &lt;/td&gt;&lt;td  &gt;德国&lt;/td&gt;&lt;td  &gt;德国&lt;/td&gt;&lt;td  &gt;销售&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;设立&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;ANKER INNOVATIONS (VIETNAM)CO., LTD. &lt;/td&gt;&lt;td  &gt;越南&lt;/td&gt;&lt;td  &gt;越南&lt;/td&gt;&lt;td  &gt;销售&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;设立&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;Anker Malta Holdings Co., Ltd. &lt;/td&gt;&lt;td  &gt;马耳他&lt;/td&gt;&lt;td  &gt;马耳他&lt;/td&gt;&lt;td  &gt;投资&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;设立&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;Anker Innovation (Malta)Co., Ltd. &lt;/td&gt;&lt;td  &gt;马耳他&lt;/td&gt;&lt;td  &gt;马耳他&lt;/td&gt;&lt;td  &gt;销售&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;设立&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;Digimarket Co., Ltd. &lt;/td&gt;&lt;td  &gt;日本&lt;/td&gt;&lt;td  &gt;日本&lt;/td&gt;&lt;td  &gt;销售&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;设立&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;Anker Innovations Australia Pty Ltd. &lt;/td&gt;&lt;td  &gt;澳大利亚&lt;/td&gt;&lt;td  &gt;澳大利亚&lt;/td&gt;&lt;td  &gt;销售&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;设立&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;Anker Store Co., Ltd. &lt;/td&gt;&lt;td  &gt;日本&lt;/td&gt;&lt;td  &gt;日本&lt;/td&gt;&lt;td  &gt;销售&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;设立&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;天津市智远管理咨询合伙企业（有限合伙）（注）&lt;/td&gt;&lt;td  &gt;天津&lt;/td&gt;&lt;td  &gt;天津&lt;/td&gt;&lt;td  &gt;投资&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;0.01% &lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;设立&lt;/td&gt;&lt;/tr&gt;
-&lt;/table&gt;</t>
-  </si>
-  <si>
-    <t>&lt;table&gt;&lt;caption&gt;七、董事、监事和高级管理人员情况1、基本情况&lt;/caption&gt;
-&lt;tr&gt;&lt;th  &gt;姓名&lt;/th&gt;&lt;th  &gt;职务&lt;/th&gt;&lt;th  &gt;任职 性别 状态&lt;/th&gt;&lt;th  &gt;年龄&lt;/th&gt;&lt;th  &gt;任期起 始日期&lt;/th&gt;&lt;th  &gt;任期终止&lt;/th&gt;&lt;th  &gt;日期&lt;/th&gt;&lt;th  &gt;期初持 股数 （股）&lt;/th&gt;&lt;th  &gt;本期增 持股份 数量 （股）&lt;/th&gt;&lt;th  &gt;本期减 持股份 数量 （股）&lt;/th&gt;&lt;th  &gt;其他 增减 变动 （股 ）&lt;/th&gt;&lt;th  &gt;期末 股份 持股 增减 数 变动 （股 的原 因&lt;/th&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;阳萌&lt;/td&gt;&lt;td  &gt;董事长&lt;/td&gt;&lt;td  &gt;现任 男&lt;/td&gt;&lt;td  &gt;41 &lt;/td&gt;&lt;td  &gt;2016年 05月 12日&lt;/td&gt;&lt;td  &gt;2025年 06月01 日&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;178,974 ,000 &lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;178,97 4,000&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;赵东平&lt;/td&gt;&lt;td  &gt;董事、 总经理&lt;/td&gt;&lt;td  &gt;现任 男&lt;/td&gt;&lt;td  &gt;47 &lt;/td&gt;&lt;td  &gt;2016年 05月 12日&lt;/td&gt;&lt;td  &gt;2025年 06月01 日&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;48,700, 000 &lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;48,700 ,000&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;张山峰&lt;/td&gt;&lt;td  &gt;董事、 副总经 理&lt;/td&gt;&lt;td  &gt;现任 男&lt;/td&gt;&lt;td  &gt;41 &lt;/td&gt;&lt;td  &gt;2016年 05月 12日&lt;/td&gt;&lt;td  &gt;2025年 06月01 日&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;6,923,0 79 &lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;6,923, 079&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;高韬&lt;/td&gt;&lt;td  &gt;董事&lt;/td&gt;&lt;td  &gt;现任 男&lt;/td&gt;&lt;td  &gt;45 &lt;/td&gt;&lt;td  &gt;2016年 05月 12日&lt;/td&gt;&lt;td  &gt;2025年 06月01 日&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;9,725,1 37 &lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;740,000 &lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;8,985,股票 137 减持&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;连萌 祝芳浩&lt;/td&gt;&lt;td  &gt;董事 董事&lt;/td&gt;&lt;td  &gt;现任 男 现任 男&lt;/td&gt;&lt;td  &gt;44  48 &lt;/td&gt;&lt;td  &gt;2017年 04月 11日 2021年 05月 27日&lt;/td&gt;&lt;td  &gt;2025年 06月01 日 2025年 06月01 日&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;邓海峰&lt;/td&gt;&lt;td  &gt;独立董 事&lt;/td&gt;&lt;td  &gt;现任 男&lt;/td&gt;&lt;td  &gt;48 &lt;/td&gt;&lt;td  &gt;2018年 01月 08日&lt;/td&gt;&lt;td  &gt;2025年 06月01 日&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;李国强 高文进&lt;/td&gt;&lt;td  &gt;独立董 事 独立董 事&lt;/td&gt;&lt;td  &gt;现任 男 现任 男&lt;/td&gt;&lt;td  &gt;44  62 &lt;/td&gt;&lt;td  &gt;2018年 01月 08日 2021年 03月 09日&lt;/td&gt;&lt;td  &gt;2024年 01月07 日 2025年 06月01 日&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;杨婷 刘枚清&lt;/td&gt;&lt;td  &gt;监事会 主席 监事&lt;/td&gt;&lt;td  &gt;现任 女 现任 女&lt;/td&gt;&lt;td  &gt;7  28 &lt;/td&gt;&lt;td  &gt;2022年 06月 02日 2022年 06月 02日&lt;/td&gt;&lt;td  &gt;2025年 06月01 日 2025年 06月01 日&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;曾旖&lt;/td&gt;&lt;td  &gt;监事&lt;/td&gt;&lt;td  &gt;现任 女&lt;/td&gt;&lt;td  &gt;30 &lt;/td&gt;&lt;td  &gt;2022年 06月 02日&lt;/td&gt;&lt;td  &gt;2025年 06月01 日&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;张希 杨帆&lt;/td&gt;&lt;td  &gt;董事会 秘书 财务负 责人&lt;/td&gt;&lt;td  &gt;现任 男 现任 男&lt;/td&gt;&lt;td  &gt;41  36 &lt;/td&gt;&lt;td  &gt;2020年 08月 27日 2021年 02月 19日&lt;/td&gt;&lt;td  &gt;2025年 06月01 日 2025年 06月01 日&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;黄思敏 毛艳红&lt;/td&gt;&lt;td  &gt;监事会 主席 监事&lt;/td&gt;&lt;td  &gt;离任 女 离任 女&lt;/td&gt;&lt;td  &gt;34  38 &lt;/td&gt;&lt;td  &gt;2019年 05月 10日 2017年 01月 11日&lt;/td&gt;&lt;td  &gt;2022年 06月02 日 2022年 06月02 日&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;2017年2022年&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;胡一杰&lt;/td&gt;&lt;td  &gt;监事&lt;/td&gt;&lt;td  &gt;离任 女&lt;/td&gt;&lt;td  &gt;37 &lt;/td&gt;&lt;td  &gt;01月&lt;/td&gt;&lt;td  &gt;06月02&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;11日&lt;/td&gt;&lt;td  &gt;日&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
-&lt;tr&gt;&lt;td  &gt;合计&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;244,322 ,216 &lt;/td&gt;&lt;td  &gt;0 &lt;/td&gt;&lt;td  &gt;740,000 &lt;/td&gt;&lt;td  &gt;0 &lt;/td&gt;&lt;td  &gt;243,58 2,216 &lt;/td&gt;&lt;/tr&gt;
-&lt;/table&gt;</t>
   </si>
 </sst>
 </file>
@@ -449,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -469,74 +406,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2">
-        <v>4.6991854</v>
-      </c>
-      <c r="D2">
-        <v>0.4292499206848461</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>2.4234862</v>
-      </c>
-      <c r="D3">
-        <v>0.3633079783843504</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4">
-        <v>3.2668607</v>
-      </c>
-      <c r="D4">
-        <v>0.09219619882783585</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5">
-        <v>1.1536229</v>
-      </c>
-      <c r="D5">
-        <v>0.02182282497345924</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>question</t>
   </si>
@@ -29,6 +29,54 @@
   </si>
   <si>
     <t>doc</t>
+  </si>
+  <si>
+    <t>关于员工佩戴工牌的规定</t>
+  </si>
+  <si>
+    <t>test_ocr</t>
+  </si>
+  <si>
+    <t>新员工入职指引在阅读这份指引前，请将您的个人正面照发给我，需要更换企业微信头像，谢谢配合！目录第一章工牌篇.3.3335. 制度查阅路径.3五、关于加班申请..44EHR系统的登陆网址及初始账号密码.4企业邮箱的登陆网址及初始账号密码.二、4共享.5三、四56第四章电脑&amp;网络篇.7第五章行政篇..停车月卡..三、8其他..四、.8第六章财务篇...9财务办公室位置.9一、二、常用流程讲解.91. CW001-财务费用报销流程..92. CW003-付款申请流程... 9第七章办公环境介绍篇.一、楼层介绍.. 10二、注意事项.第八章常用联系人篇....11一、人事方面疑问接口.. 11二、员工关系科（公司相关协会的了解）接口.. 1112..12.. 1212.12作用..13操作指引.13新员工入职指引第一章工牌篇一、关于工牌的主要用途1. 作为赛维员工的标识。康利城6 号楼均属于公司范围，因此，在进入本栋楼时，需戴好工牌。2. 作为出入公司闸机、电梯的工具。公司每层楼进入办公区都需要刷工牌进入/出去，且一卡一刷；乘坐电梯前往每层楼都需要刷工牌，在办公区域的电梯共有六部，只有2 号电梯、6 号电梯属于双层电梯，其他四部属于单层电梯，但一楼、五楼属于公共区域，六部电梯均可到达；靠近楼梯间里面有两部货梯，其中靠里面的货梯才可使用，每一层均可停留，也需要刷工牌乘坐。3. 作为在食堂就餐的饭卡使用。食宿补贴是直接发放到工资里的，在食堂消费需要另行充值。二、工牌的补办流程及收费标准工牌卡、卡套、绳子丢失或损坏，补办路径：EHR-流程-流程申请-行政-【XZ012-工牌卡片/卡套/吊绳补办申请流程】，具体收费标准见流程申请页，如有疑问可以企业微信咨询彭诗园。1. 进入公司范围内必须正确佩戴工牌，不能拿在手上，行政部抓到一次需要乐捐100 元作为部门的活动经费；2. 为了保障公司信息安全，公司的所有闸机都严禁代刷，行政部的同事抓到一次扣款50 元；3. 借用临时工牌当天下班需要将工牌归还至1 楼前台，未及时归还的，将给予100 元的罚款。四、饭卡充值2. 饭卡充值方式：10 楼财务&amp;风控办公室里面的小办公室（10A20）找陈燕芬/张小洁/杨秀梅；饭卡充值仅支持微信和现金。</t>
+  </si>
+  <si>
+    <t>New Employee Onboarding Guide
+一、关
+于工牌的主要用途.
+二、
+工牌的补办流程及收费标准
+三、
+工牌的相关管理条例（提炼，详版见附件）
+四、
+饭卡充值.
+2
+2
+一、打卡机位置及重新录入指纹.
+2
+二、
+个人考勤的查看路径.
+2
+三、
+请假流程路径.
+2
+四、
+考勤相关规则.
+. 3
+1. 入职当天考勤.
+2. 补卡..
+3. 弹性..
+4. 免费打车.
+第三章系统篇..</t>
+  </si>
+  <si>
+    <t>三、工牌的相关管理条例（提炼，详版见附件）
+补办类型请选择
+请选择
+只要卡片 (20元)
+只要卡套（5元）
+只要吊绳（5元）
+卡片+卡套+吊绳（30元）
+卡套+吊绳(10元)</t>
   </si>
 </sst>
 </file>
@@ -386,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -406,6 +454,57 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>22.598667</v>
+      </c>
+      <c r="D2">
+        <v>0.7379143205612128</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>15.089769</v>
+      </c>
+      <c r="D3">
+        <v>0.452475441383179</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>9.023721</v>
+      </c>
+      <c r="D4">
+        <v>0.3270232115864122</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="20">
   <si>
     <t>question</t>
   </si>
@@ -31,10 +31,38 @@
     <t>doc</t>
   </si>
   <si>
-    <t>关于员工佩戴工牌的规定</t>
+    <t>工牌丢了怎么办</t>
+  </si>
+  <si>
+    <t>工牌补办要多少钱</t>
+  </si>
+  <si>
+    <t>员工离职流程是怎样的</t>
+  </si>
+  <si>
+    <t>驻外人员有什么福利</t>
+  </si>
+  <si>
+    <t>外派人员怎么打卡</t>
+  </si>
+  <si>
+    <t>我昨天加班到9：20，今天可以几点打卡上班？</t>
+  </si>
+  <si>
+    <t>周五加班到10点，下周一可以弹性打卡上班么？</t>
   </si>
   <si>
     <t>test_ocr</t>
+  </si>
+  <si>
+    <t>三、工牌的相关管理条例（提炼，详版见附件）
+补办类型请选择
+请选择
+只要卡片 (20元)
+只要卡套（5元）
+只要吊绳（5元）
+卡片+卡套+吊绳（30元）
+卡套+吊绳(10元)</t>
   </si>
   <si>
     <t>新员工入职指引在阅读这份指引前，请将您的个人正面照发给我，需要更换企业微信头像，谢谢配合！目录第一章工牌篇.3.3335. 制度查阅路径.3五、关于加班申请..44EHR系统的登陆网址及初始账号密码.4企业邮箱的登陆网址及初始账号密码.二、4共享.5三、四56第四章电脑&amp;网络篇.7第五章行政篇..停车月卡..三、8其他..四、.8第六章财务篇...9财务办公室位置.9一、二、常用流程讲解.91. CW001-财务费用报销流程..92. CW003-付款申请流程... 9第七章办公环境介绍篇.一、楼层介绍.. 10二、注意事项.第八章常用联系人篇....11一、人事方面疑问接口.. 11二、员工关系科（公司相关协会的了解）接口.. 1112..12.. 1212.12作用..13操作指引.13新员工入职指引第一章工牌篇一、关于工牌的主要用途1. 作为赛维员工的标识。康利城6 号楼均属于公司范围，因此，在进入本栋楼时，需戴好工牌。2. 作为出入公司闸机、电梯的工具。公司每层楼进入办公区都需要刷工牌进入/出去，且一卡一刷；乘坐电梯前往每层楼都需要刷工牌，在办公区域的电梯共有六部，只有2 号电梯、6 号电梯属于双层电梯，其他四部属于单层电梯，但一楼、五楼属于公共区域，六部电梯均可到达；靠近楼梯间里面有两部货梯，其中靠里面的货梯才可使用，每一层均可停留，也需要刷工牌乘坐。3. 作为在食堂就餐的饭卡使用。食宿补贴是直接发放到工资里的，在食堂消费需要另行充值。二、工牌的补办流程及收费标准工牌卡、卡套、绳子丢失或损坏，补办路径：EHR-流程-流程申请-行政-【XZ012-工牌卡片/卡套/吊绳补办申请流程】，具体收费标准见流程申请页，如有疑问可以企业微信咨询彭诗园。1. 进入公司范围内必须正确佩戴工牌，不能拿在手上，行政部抓到一次需要乐捐100 元作为部门的活动经费；2. 为了保障公司信息安全，公司的所有闸机都严禁代刷，行政部的同事抓到一次扣款50 元；3. 借用临时工牌当天下班需要将工牌归还至1 楼前台，未及时归还的，将给予100 元的罚款。四、饭卡充值2. 饭卡充值方式：10 楼财务&amp;风控办公室里面的小办公室（10A20）找陈燕芬/张小洁/杨秀梅；饭卡充值仅支持微信和现金。</t>
@@ -69,14 +97,40 @@
 第三章系统篇..</t>
   </si>
   <si>
-    <t>三、工牌的相关管理条例（提炼，详版见附件）
-补办类型请选择
-请选择
-只要卡片 (20元)
-只要卡套（5元）
-只要吊绳（5元）
-卡片+卡套+吊绳（30元）
-卡套+吊绳(10元)</t>
+    <t>四、其他如需领取电脑配件（鼠标、键盘）或者更换电脑及配件，请在企业微信提前联系---网络运维部(杨妙虹、丁武专、彭维明、王振民)，确定是否可以更换。第7 页第五章行政篇一、公司宿舍入住&amp;退宿手续办理EHR 系统-流程申请-【XZ006 宿舍管理流程】,提交流程后在企业微信联系行政部-梁梅婷（10 楼行政办公区，10A20 门口，茶水间旁边），宿舍的具体地址及情况在企业微信联系行政部-梁梅婷。二、班车乘坐&amp;取消手续办理EHR 系统-流程申请-【XZ003 班车管理流程】，提交后找行政部-梁梅婷领取&amp;归还乘车证。具体路线以EHR 系统班车管理流程里的为准，乘车前记得要找行政部-梁梅婷拿到乘车证才可乘车。三、停车月卡康利城停车月卡事项（自行办理，公司不代办）联系电话：0755-28281137；证、身份证（均为复印件）、工牌；收费：300 元/月；四、其他办公环境遇到问题，如空调机漏水、茶水间的微波炉和直饮水有问题、卫生环境、桌椅损坏、工位插座没电等情况，均可在企业微信联系行政部-陈东妮，讲清楚问题及对应的位置。打印机没墨或者故障：行政部-梁梅婷；第8 页一、财务办公室位置十楼背对前台右转至尽头。二、常用流程讲解1. CW001-财务费用报销流程使用情况：员工因工作需要自行付款，后面申请报销。（例如需后续报活动经费的部门聚餐费用、出差时产生的差旅费、交通费等）详细操作可见指引。2. CW003-付款申请流程使用情况：需直接付款给供应商或者客户，非员工付款的情况。详细操作可见指引。3. 公司的所有报销必须提供发票，收据是不可以作为报销的依据的！发票抬头和纳税人识别号可咨询导师！第9 页第七章办公环境介绍篇一、楼层介绍二、注意事项1. 空调遥控器用完后请及时归还至空调卡槽处，勿随意放置；2. 中午12:00-13:30 为午休时间，12:40-13:30 请勿在办公环境内发出声音，影响其他同事休息，尽可能避免这段时间内使用茶水间；3. 微波炉、冰箱属于共用资产，请各位按照要求使用，切勿损人不利己；4. 会议室的空调在结束会议时记得及时关闭！5. 打印机没纸了请自行添加，如打印纸快用完请联系部门助理；6. 打印机的连接、网络问题：请联系网络运维部-丁武专/王振民/彭维明；7. 办公用品的领取：部门助理；</t>
+  </si>
+  <si>
+    <t>位置..
+一、
+二、
+对接人
+7
+三、
+电脑等固定资产的接收
+四、
+其他..
+.7
+.8
+公司宿舍入住&amp;退宿手续办理
+8
+二、
+班车乘坐&amp;取消手续办理.
+8</t>
+  </si>
+  <si>
+    <t>第二章考勤篇一、打卡机位置及重新录入指纹公司目前除了五楼之外均设有打卡机，如其中一台打不上可选择其他楼层的打卡机打卡；打卡机指纹重新录入接口：部门助理/人事部-但婷婷；二、个人考勤的查看路径EHR 系统-个人办公-我的考勤-我的考勤表三、请假流程路径补卡、请假、销假流程的申请路径：EHR-流程-流程申请-考勤-【HR053-考勤补卡申请流程】/【HR051-请假申请流程】/【HR054-销假申请流程】/【HR052-出差外出公干申请流程】；四、考勤相关规则1. 入职当天考勤2. 补卡考勤以打卡录入为准，打卡建议多打几次，根据公司相关的制度，每月享受2 次补卡机会，超出补卡机会的需要请假，缺上班卡请一上午（9:00-12:00，即3H），缺下班卡请一下午,13:30-18:00，即4.5H）；3. 弹性工作日加班超过21:00，次日上班卡可享受弹性（第二天上午请假、漏卡除外），最晚下班打卡时间对应第二日弹性上班卡时间如下图所示。入职当天的上班卡不用管，HR 后面处理考勤表时会统一处理！注意：弹性上班打卡不用提交电子流程，系统自动设置弹性时长。工作日加班至22:00 可以直接使用滴滴商旅打车回家，打车路径：企业微信---工作台---滴滴商旅。具体操作指南见《员工使用手册》第4 部分---“用车预定流程”。市外出差、市内外出需要提前在E-HR 系统提交HR057-出差外出公干申请流程（滴滴商旅），待流程审批完成后再登录滴滴商旅平台打车、或进行机票购买与酒店预定。具体操作指引见《员工使用手册》。5. 制度查阅路径EHR 系统---资源文件---文档---文档中心---人力资源规章制度---4. 免费打车《SD-ZD-HR-007 考勤管理制度》。五、关于加班申请周末或者节假日的加班必须由部门经理提前发起邮件申请。发给部门总监/VP，然后抄送给艾帆、寻佑兰、但婷婷和部门助理，说清楚加班的日期和人员及原因。然后让部门总监在邮件里回复审批。部门无经理，则由部门总监发起，VP 回复审批。邮件均需提前发起，加班当天需正常打上下班卡点，如有卡点缺失，将对调休时长折算处理。重点提示：加班时一定记得打上、下班卡，未正常打卡将影响调休时长！第三章系统篇一、EHR系统的登陆网址及初始账号密码</t>
+  </si>
+  <si>
+    <t>&lt;table&gt;
+&lt;tr&gt;&lt;td  &gt;最晚下班打卡&lt;/td&gt;&lt;td  &gt;21:00&lt;A≤&lt;/td&gt;&lt;td  &gt;22:00&lt;A 23:00&lt;A≤24:00&lt;A≤&lt;/td&gt;&lt;td  &gt;02:00&lt;A≤&lt;/td&gt;&lt;td  &gt;04:00&lt;A≤&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td  &gt;时间（A） 弹性上班打卡时间&lt;/td&gt;&lt;td  &gt;22:00&lt;/td&gt;&lt;td  &gt;≤23: 0024: 00 02:00&lt;/td&gt;&lt;td  &gt;04:00&lt;/td&gt;&lt;td  rowspan=5 &gt;06:00&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td  &gt;第二天9:30&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td  &gt;第二天10:00&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td  &gt;第二天11:00&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td  &gt;第二天13:30&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td  &gt;当天下午14:00&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td  &gt;当天下午15:00&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td  &gt;O&lt;/td&gt;&lt;/tr&gt;
+&lt;/table&gt;</t>
   </si>
 </sst>
 </file>
@@ -434,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -459,16 +513,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C2">
-        <v>22.598667</v>
+        <v>0.83291245</v>
       </c>
       <c r="D2">
-        <v>0.7379143205612128</v>
+        <v>0.9086178969328287</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -476,16 +530,16 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>15.089769</v>
+        <v>0.80842984</v>
       </c>
       <c r="D3">
-        <v>0.452475441383179</v>
+        <v>0.7232117371867114</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -493,16 +547,203 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>0.81084245</v>
+      </c>
+      <c r="D4">
+        <v>0.3050758672156551</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>0.7544061</v>
+      </c>
+      <c r="D5">
+        <v>0.1066905939456512</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="C4">
-        <v>9.023721</v>
-      </c>
-      <c r="D4">
-        <v>0.3270232115864122</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>27.181269</v>
+      </c>
+      <c r="D6">
+        <v>0.9826909042463318</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>30.125782</v>
+      </c>
+      <c r="D7">
+        <v>0.552660427431561</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>14.733977</v>
+      </c>
+      <c r="D8">
+        <v>0.05602938511788175</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9">
+        <v>0.77135646</v>
+      </c>
+      <c r="D9">
+        <v>0.1061334359169432</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>0.702247</v>
+      </c>
+      <c r="D10">
+        <v>0.1316190483557701</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
         <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11">
+        <v>24.331974</v>
+      </c>
+      <c r="D11">
+        <v>0.1395135742749575</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>35.962063</v>
+      </c>
+      <c r="D12">
+        <v>0.8240375258202992</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>53.982674</v>
+      </c>
+      <c r="D13">
+        <v>0.7039566617217692</v>
+      </c>
+      <c r="E13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14">
+        <v>58.86583</v>
+      </c>
+      <c r="D14">
+        <v>0.6049825160054898</v>
+      </c>
+      <c r="E14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>35.352142</v>
+      </c>
+      <c r="D15">
+        <v>0.4741898319393823</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
